--- a/submissions/2A202602978_NguyenDucTrieu/results.xlsx
+++ b/submissions/2A202602978_NguyenDucTrieu/results.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Backbones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Training" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Inference" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Final" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="PerClass" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Latency" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backbones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Training" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inference" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PerClass" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Latency" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Backbones'!$A$1:$M$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Training'!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Inference'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Final'!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PerClass'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Latency'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Summary'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Backbones'!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Training'!$A$1:$K$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Inference'!$A$1:$L$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Final'!$A$1:$K$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PerClass'!$A$1:$G$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Latency'!$A$1:$L$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Summary'!$A$1:$F$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,8 +30,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,10 +43,13 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -56,8 +61,13 @@
         <fgColor rgb="00234E70"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F5E3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -65,13 +75,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,22 +458,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="41" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,8 +543,253 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>B01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>a1_in1k</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>23.526473</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>4.131713024</v>
+      </c>
+      <c r="F2" t="n">
+        <v>224</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0.8045168183298181</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0.8568980291345329</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>56.35913529108331</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>5.72551949994704</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>THOP estimate; unsupported ops excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>resnext50_32x4d</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>a1h_in1k</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>22.998345</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>4.286154752</v>
+      </c>
+      <c r="F3" t="n">
+        <v>224</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0.6786930361803244</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0.7400742644958583</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>76.5960052605833</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>7.824952999953894</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>THOP estimate; unsupported ops excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>B03</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>in12k_ft_in1k</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>27.827049</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>4.454808576</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0.9694980271641158</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>0.9768637532133676</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>69.53567289275001</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>5.825474999937796</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>THOP estimate; unsupported ops excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>deit_small_patch16_224</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>fb_in1k</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>21.669129</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>4.240838016</v>
+      </c>
+      <c r="F5" t="n">
+        <v>224</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0.9504043877708129</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.9651528134818623</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>48.53606735800008</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>5.427051999959076</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>THOP estimate; unsupported ops excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>efficientnet_b0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ra_in1k</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>4.019077</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.384610272</v>
+      </c>
+      <c r="F6" t="n">
+        <v>224</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0.7935112372741008</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.8463296201085404</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>35.80667670733328</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>8.049749999827327</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>THOP estimate; unsupported ops excluded</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M1"/>
+  <autoFilter ref="A1:M6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -534,20 +800,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -607,8 +873,548 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.9694980271641158</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.9768637532133676</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0.9594594594594594</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0.9382716049382716</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Screening: one seed; no significance claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0.9696652910096901</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0.976006855184233</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0.0001672638455743058</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0.9480812641083521</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>0.9343065693430657</v>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Screening: one seed; no significance claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.9687954774927968</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.9757212225078549</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>-0.0007025496713189971</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0.9411764705882352</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.935560859188544</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Screening: one seed; no significance claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{"init": "scratch"}</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.3326751251400383</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.580405598400457</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>-0.6368229020240775</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.3109540636042403</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Screening: one seed; no significance claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{"init": "frozen"}</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.8524954953716382</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.8831762353613254</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>-0.1170025317924777</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0.817351598173516</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.7751937984496123</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Screening: one seed; no significance claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{"aug": "color"}</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.9680185591311896</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.9757212225078549</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>-0.001479468032926201</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0.9454545454545454</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.9356435643564357</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Screening: one seed; no significance claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{"mix": "mixup"}</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.9683328337131439</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.9757212225078549</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>-0.00116519345097188</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.9406392694063926</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.9268292682926828</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Screening: one seed; no significance claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{"mix": "cutmix"}</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.9635854218533891</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.9714367323621822</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>-0.005912605310726682</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0.9255813953488371</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.9125295508274232</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Screening: one seed; no significance claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{"loss": "ls", "label_smoothing": 0.1}</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.9683934336585405</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0.976006855184233</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>-0.001104593505575346</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0.9478458049886621</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0.9292929292929292</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Screening: one seed; no significance claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{"loss": "focal"}</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0.9666692732905813</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0.9740074264495858</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>-0.00282875387353454</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0.9538461538461539</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0.926208651399491</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Screening: one seed; no significance claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{"loss": "ce_weighted"}</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.9659902950706371</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0.9731505284204514</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>-0.003507732093478766</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0.9617977528089887</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.9197080291970803</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Screening: one seed; no significance claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>combination</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.9694980271641158</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0.9768637532133676</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0.9594594594594594</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.9382716049382716</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Screening: one seed; no significance claim</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:K13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -619,21 +1425,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -698,8 +1504,228 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>I00</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>/kaggle/working/runs/T00/seed0/best.pt</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.9694980271641158</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.9768637532133676</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.01151650537936497</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>5.99133699961385</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>6.488325900591008</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>6.813236659727409</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>199.3826440432193</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>I01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>hflip_prob</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>/kaggle/working/runs/T00/seed0/best.pt</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.9696825122862845</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.9774350185661239</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.008767381033806174</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>12.2846855001626</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>13.23104654875351</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>13.73565331092323</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>111.0700437339999</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>2.05040803095442</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>I02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hflip_logit</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>/kaggle/working/runs/T00/seed0/best.pt</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.9696825122862845</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.9774350185661239</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.0100093464686577</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>11.82362199961062</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>12.58216840005844</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>12.79296507018444</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>109.7670100706689</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>1.973453003957659</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>I03</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>fivecrop</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>/kaggle/working/runs/T00/seed0/best.pt</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.9714040866938549</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.9782919165952585</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0.00800042111033953</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>30.90934850024496</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>32.48860809944745</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>33.62022701076057</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>43.21842614243531</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>5.159006829733849</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>I04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>temperature</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>/kaggle/working/runs/T00/seed0/best.pt</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.9694980271641158</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.9768637532133676</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.005107227682011819</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>5.855644499206392</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>6.027183900823729</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>6.434181579206785</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>215.2513570978207</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0.9773518831579322</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -710,19 +1736,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -783,8 +1809,276 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>convnext_tiny / ce / basic / single</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.9694980271641158</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.9704105208099756</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.9771884801824922</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.009369457536355897</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>convnext_tiny / ce / basic / single</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.9696652910096901</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.9727446470788134</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.9786142001710864</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.01031583518391784</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>convnext_tiny / ce / basic / single</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.9687954774927968</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.96903171172224</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.9760479041916168</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.008706693122326793</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>convnext_tiny / ce / basic / single</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>mean ± std (ddof=1)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.9693195985555342</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.970728959870343</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.9772835281817317</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.009463995280866841</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.001876839049279101</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0.00128578550123261</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.0008087259006908839</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>convnext_tiny / ce / basic / fivecrop</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.9714040866938549</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.9708403869831902</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.9780439121756487</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.01106901089820355</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>convnext_tiny / ce / basic / fivecrop</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.9702624205016009</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.9754459419922967</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.9808953521528372</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.008073121060735586</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>convnext_tiny / ce / basic / fivecrop</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.9718247989179987</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0.9729212358123456</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.979469632164243</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0.00775374568577132</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>convnext_tiny / ce / basic / fivecrop</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean ± std (ddof=1)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.9711637687044848</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.9730691882626109</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.979469632164243</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.00896529254823682</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.002306339454878919</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0.001425719988594254</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.001828858477171883</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:K9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -795,16 +2089,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -844,8 +2138,1466 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Chinee Apple</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>226</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.9601769911504425</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.9601769911504425</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.9601769911504425</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Lantana</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>213</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.9765258215962441</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.9765258215962441</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.9765258215962441</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Parkinsonia</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>207</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.9490740740740741</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.9903381642512077</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.9692671394799054</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Parthenium</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>205</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.9949238578680203</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.9560975609756097</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.9751243781094527</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Prickly Acacia</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>213</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.9203539823008849</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.9765258215962441</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.9476082004555809</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Rubber Vine</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>202</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.9801980198019802</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.9850746268656716</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Siam Weed</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>215</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.9815668202764977</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.9906976744186047</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.9861111111111112</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Snake Weed</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>204</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.9507389162561576</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.946078431372549</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.9484029484029484</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Negatives</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1822</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0.9889441680486457</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.9818880351262349</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0.9854034701184247</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Chinee Apple</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>226</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0.958904109589041</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0.9292035398230089</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0.9438202247191011</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Lantana</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>213</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.9765258215962441</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0.985781990521327</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Parkinsonia</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>207</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0.9806763285024155</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.9806763285024155</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0.9806763285024155</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Parthenium</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>205</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0.9901960784313726</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.9853658536585366</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0.9877750611246944</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Prickly Acacia</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>213</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0.9327354260089686</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0.9765258215962441</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0.9541284403669725</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Rubber Vine</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>202</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.9752475247524752</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0.9874686716791979</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Siam Weed</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>215</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>0.9684684684684685</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>0.9839816933638443</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Snake Weed</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>204</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0.9209302325581395</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0.9705882352941176</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0.9451073985680192</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Negatives</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1822</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0.9889563776918829</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0.9829857299670691</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>0.985962014863749</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Chinee Apple</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>226</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0.963302752293578</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0.9292035398230089</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>0.9459459459459459</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Lantana</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>213</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0.9674418604651163</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>0.9765258215962441</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>0.9719626168224299</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Parkinsonia</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>207</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0.9852941176470589</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0.9710144927536232</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>0.9781021897810219</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Parthenium</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>205</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>0.9901477832512315</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>0.9804878048780488</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>0.9852941176470588</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Prickly Acacia</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>213</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0.9241071428571429</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0.971830985915493</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0.9473684210526317</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Rubber Vine</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>202</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0.9900990099009901</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0.9900990099009901</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>0.9900990099009901</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Siam Weed</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>215</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0.9594594594594594</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0.9906976744186047</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0.9748283752860413</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Snake Weed</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>204</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0.9705882352941176</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>0.9428571428571428</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Negatives</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1822</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0.9900166389351082</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0.9796926454445664</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0.9848275862068966</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Chinee Apple</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>226</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>0.9557522123893806</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>0.957871396895787</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Lantana</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>213</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0.9904306220095693</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0.971830985915493</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0.981042654028436</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Parkinsonia</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>207</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0.9577464788732394</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0.9855072463768116</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0.9714285714285714</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Parthenium</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>205</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0.9949238578680203</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.9560975609756097</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0.9751243781094527</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Prickly Acacia</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>213</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>0.9162995594713657</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>0.9765258215962441</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0.9454545454545455</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Rubber Vine</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>202</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0.9899497487437185</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0.9752475247524752</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0.9825436408977556</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Siam Weed</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>215</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>0.9906976744186047</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>0.9906976744186047</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>0.9906976744186047</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Snake Weed</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>204</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0.9558823529411765</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0.9466019417475728</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Negatives</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1822</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>0.9889746416758545</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>0.9846322722283205</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>0.9867986798679869</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Chinee Apple</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>226</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>0.9769585253456221</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0.9380530973451328</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0.9571106094808127</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Lantana</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>213</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>0.9951923076923077</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>0.971830985915493</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>0.983372921615202</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Parkinsonia</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>207</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>0.9854368932038835</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0.9806763285024155</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0.9830508474576272</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Parthenium</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>205</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>0.9901960784313726</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>0.9853658536585366</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>0.9877750611246944</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Prickly Acacia</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>213</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>0.9330357142857143</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>0.9812206572769953</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>0.9565217391304348</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Rubber Vine</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>202</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>0.9801980198019802</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Siam Weed</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>215</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>0.9727272727272728</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0.9953488372093023</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>0.9839080459770115</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Snake Weed</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>204</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>0.9295774647887324</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>0.9705882352941176</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>0.9496402877697842</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Negatives</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1822</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>0.9889928453494772</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0.9862788144895719</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>0.9876339653751031</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Chinee Apple</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>226</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>0.967741935483871</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>0.9292035398230089</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>0.9480812641083521</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Lantana</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>213</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>0.9811320754716981</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0.9765258215962441</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>0.9788235294117646</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Parkinsonia</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>207</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>0.9805825242718447</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>0.9758454106280193</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>0.9782082324455206</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Parthenium</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>205</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>0.9852941176470589</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>0.9804878048780488</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>0.9828850855745721</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Prickly Acacia</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>213</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>0.9327354260089686</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>0.9765258215962441</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>0.9541284403669725</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Rubber Vine</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>202</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>0.9950248756218906</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>0.9900990099009901</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>0.9925558312655087</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Siam Weed</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>215</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>0.9638009049773756</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>0.9906976744186047</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>0.9770642201834864</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Snake Weed</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>204</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>0.9345794392523364</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>0.9803921568627451</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>0.9569377990430622</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Negatives</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1822</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>0.9911553344389166</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>0.9840834248079035</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>0.98760671991187</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:G55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -856,7 +3608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -865,10 +3617,10 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
@@ -935,8 +3687,1388 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>B01_seed0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>224</v>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>5.72551949994704</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>6.110806399919966</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>6.678987500113183</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>174.6566403291876</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B02_seed0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>224</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>7.824952999953894</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>8.498713300082272</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>8.705717580292005</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>127.7962947516608</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B03_seed0</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>224</v>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>5.825474999937796</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>9.349906199940961</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>9.361236329909843</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>171.6598217331081</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B04_seed0</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>224</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>5.427051999959076</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>5.636517350330904</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>6.737120570096528</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>184.2621003092546</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B05_seed0</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>224</v>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>8.049749999827327</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>8.537951349853756</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>9.266419500045233</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>124.2274604828039</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F01_seed0</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>224</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>5.830468499880226</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>6.025357099224493</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>6.184504508983082</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>171.5128038202321</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F01_seed1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>224</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>6.123441502495552</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>6.782447852310725</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>7.068415159119472</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>163.3068593196259</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F01_seed2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>224</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>6.428717500966741</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>7.162751248870335</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>7.643654849416635</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>155.552021044574</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T00_seed0</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>224</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>5.834838500049955</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>6.115693550145807</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>6.284591889525476</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>171.384349368271</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T00_seed1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>224</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>6.279177499891375</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>6.808951249149686</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>7.177431960735705</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>159.2565268329012</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T00_seed2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>224</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>5.824976000440074</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>6.328871049936424</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>6.997991370517413</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>171.6745270580429</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T01_seed0</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>224</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>5.828806999943481</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>5.983078200233649</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>6.318306380144351</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>171.561693500865</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T02_seed0</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>224</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>5.853903000115679</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>8.835557550128215</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>9.874623159530532</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>170.8261992008134</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T03_seed0</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>224</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>6.387223000274389</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>7.074564000186001</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>7.371259889987418</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>156.5625624715218</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T04_seed0</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>224</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>5.833096499372914</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>5.985335850436968</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>6.184758591571163</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>171.4355317295891</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T05_seed0</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>224</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>5.834570500155678</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>6.009232000633347</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>6.13596319928547</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>171.3922215822601</v>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T06_seed0</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>224</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>5.841730000611278</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>6.325015299262304</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>7.200840449859244</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>171.1821669086658</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T07_seed0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>224</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>5.870960500033107</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>6.268003548939305</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>6.380727810610558</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>170.329880433425</v>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T08_seed0</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>224</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>5.832460500641901</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>5.972754300364613</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>6.141540188746149</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>171.4542258605855</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T09_seed0</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>224</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>6.297570000242558</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>7.001306950951403</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>7.964407359504553</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>158.7914068381112</v>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>I00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>224</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>5.99133699961385</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>6.488325900591008</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>6.813236659727409</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>166.9076535111364</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>I00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>32</v>
+      </c>
+      <c r="E23" t="n">
+        <v>224</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>160.4954139993424</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>163.2444315001521</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>163.6288514707849</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>199.3826440432193</v>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>I01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>224</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>12.2846855001626</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>13.23104654875351</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>13.73565331092323</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>81.40216532094081</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>I01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>32</v>
+      </c>
+      <c r="E25" t="n">
+        <v>224</v>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>288.1064859993785</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>297.1884136994959</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>297.8295259489641</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>111.0700437339999</v>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>I02</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>224</v>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>11.82362199961062</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>12.58216840005844</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>12.79296507018444</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>84.57645212549353</v>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>I02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>32</v>
+      </c>
+      <c r="E27" t="n">
+        <v>224</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>291.5265705005368</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>297.3110070004623</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>297.9687771599492</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>109.7670100706689</v>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>I03</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>256</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>30.90934850024496</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>32.48860809944745</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>33.62022701076057</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>32.35267155475874</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>I03</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>32</v>
+      </c>
+      <c r="E29" t="n">
+        <v>256</v>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>740.4249265009639</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>745.2109968001423</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>748.5265215110667</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>43.21842614243531</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>I04</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>224</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>5.855644499206392</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>6.027183900823729</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>6.434181579206785</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>170.7753946018289</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>I04</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>32</v>
+      </c>
+      <c r="E31" t="n">
+        <v>224</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>148.6634065004182</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>150.199709199569</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>150.9689944201637</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>215.2513570978207</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -947,15 +5079,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -990,8 +5122,248 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>0.9718247989179987</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0.9782919165952585</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>6.428717500966741</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>1-view train checkpoint; validation only</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0.9714040866938549</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.9782919165952585</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>5.830468499880226</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1-view train checkpoint; validation only</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>I03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0.9714040866938549</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.9782919165952585</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>30.90934850024496</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>fivecrop</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0.9702624205016009</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.9765781205369894</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>6.123441502495552</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1-view train checkpoint; validation only</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>I01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0.9696825122862845</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.9774350185661239</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>12.2846855001626</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hflip_prob</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>I02</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0.9696825122862845</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.9774350185661239</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>11.82362199961062</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>hflip_logit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0.9696652910096901</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.976006855184233</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>6.279177499891375</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1-view train checkpoint; validation only</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>0.9694980271641158</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.9768637532133676</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>5.834838500049955</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1-view train checkpoint; validation only</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>B03</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0.9694980271641158</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.9768637532133676</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>5.825474999937796</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1-view train checkpoint; validation only</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>I00</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>0.9694980271641158</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.9768637532133676</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>5.99133699961385</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>